--- a/volumes/02-solar-home-systems/templates/AEF_V2_T02_Due_Diligence_Checklist.xlsx
+++ b/volumes/02-solar-home-systems/templates/AEF_V2_T02_Due_Diligence_Checklist.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist'!$A$6:$K$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist'!$A$6:$K$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -647,7 +647,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T02  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T02  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -792,7 +792,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Links to the Volume 2 model and book</t>
+          <t>Links to Book 2 and MODEL 2</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -841,7 +841,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the fictional SolaraPay case where data are needed. (c) 2026 Emmanuel Boujieka Kamga.</t>
+          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the book's worked examples or to the fictional SolaraPay case. (c) 2026 Emmanuel Boujieka Kamga.</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T02&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T02 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -879,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -898,7 +898,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -949,7 +949,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T02  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T02  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Collection rate definition</t>
+          <t>Collection rate definition (operational metric)</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>KPI definitions aligned with PAYGo PERFORM</t>
+          <t>Written definition; deposits excluded from both sides</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Deposits included in the numerator</t>
+          <t>Deposits included in the numerator, or the collection rate presented as the PERFORM repayment rate</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Restructuring and re-ageing</t>
+          <t>PAYGo PERFORM 2026 KPIs</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Restructuring log with dates</t>
+          <t>RR PvP, RR PvFin, RR PvP at 90 days, RR PvP at 2x term and OR @2x computed on contract data under the GOGLA Technical Guide (June 2026)</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Re-ageing clustered before reporting or covenant dates</t>
+          <t>KPIs not computed, rebuilt from monthly data, or averaged across cohorts instead of summing numerators and denominators</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1534,7 +1534,7 @@
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="16" t="n"/>
       <c r="K18" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Write off policy and history</t>
+          <t>Restructuring and re-ageing</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Policy with version dates; write off file</t>
+          <t>Restructuring log with dates</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Policy changed during the history period</t>
+          <t>Re-ageing clustered before reporting or covenant dates</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -1577,7 +1577,7 @@
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Repossession and resale outcomes</t>
+          <t>Write off policy and history</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Repossession log; resale proceeds and costs</t>
+          <t>Policy with version dates; write off file</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Recovery assumptions above observed proceeds</t>
+          <t>Policy changed during the history period</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Recalibration of plan curves</t>
+          <t>Repossession and resale outcomes</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Analyst calibration workpaper</t>
+          <t>Repossession log; resale proceeds and costs</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Plan hazards below observed hazards</t>
+          <t>Recovery assumptions above observed proceeds</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1663,38 +1663,38 @@
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>OP01</t>
+          <t>CR11</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Operations and agents</t>
+          <t>Credit and data tape</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Agent register and productivity</t>
+          <t>Recalibration of plan curves</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Agent list with sales and cohort quality</t>
+          <t>Analyst calibration workpaper</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Sales concentrated in a few agents or regions</t>
+          <t>Plan hazards below observed hazards</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1706,13 +1706,13 @@
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>OP02</t>
+          <t>OP01</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -1722,22 +1722,22 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Commission structure and clawbacks</t>
+          <t>Agent register and productivity</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Commission plans; clawback records</t>
+          <t>Agent list with sales and cohort quality</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>No repayment linked component, or clawbacks never applied</t>
+          <t>Sales concentrated in a few agents or regions</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>OP03</t>
+          <t>OP02</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Fraud controls</t>
+          <t>Commission structure and clawbacks</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Verification call logs; field audit reports</t>
+          <t>Commission plans; clawback records</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>No fraud losses ever recorded</t>
+          <t>No repayment linked component, or clawbacks never applied</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>OP04</t>
+          <t>OP03</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Installation and after sales service</t>
+          <t>Fraud controls</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Service tickets and turnaround times</t>
+          <t>Verification call logs; field audit reports</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Rising unresolved tickets</t>
+          <t>No fraud losses ever recorded</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1835,13 +1835,13 @@
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="16" t="n"/>
       <c r="K25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>OP05</t>
+          <t>OP04</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Inventory and supplier terms</t>
+          <t>Installation and after sales service</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Stock reports; supplier contracts</t>
+          <t>Service tickets and turnaround times</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Supplier credit shortening</t>
+          <t>Rising unresolved tickets</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -1878,38 +1878,38 @@
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="16" t="n"/>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>TL01</t>
+          <t>OP05</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Technology and lockout</t>
+          <t>Operations and agents</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Lockout platform design and access control</t>
+          <t>Inventory and supplier terms</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Platform description; user access rights</t>
+          <t>Stock reports; supplier contracts</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Unlock codes issued without audit trail</t>
+          <t>Supplier credit shortening</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -1921,13 +1921,13 @@
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="16" t="n"/>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>TL02</t>
+          <t>TL01</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Unlocks reconciled to payments</t>
+          <t>Lockout platform design and access control</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Unlock log against payment records</t>
+          <t>Platform description; user access rights</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Rising share of unlocks without full payment</t>
+          <t>Unlock codes issued without audit trail</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>TL03</t>
+          <t>TL02</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Tampering and bypass rate</t>
+          <t>Unlocks reconciled to payments</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Device telemetry reports</t>
+          <t>Unlock log against payment records</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Bypass rate not measured</t>
+          <t>Rising share of unlocks without full payment</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>TL04</t>
+          <t>TL03</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
@@ -2023,22 +2023,22 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Mobile money integration and reconciliation</t>
+          <t>Tampering and bypass rate</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Payment platform to ledger reconciliation</t>
+          <t>Device telemetry reports</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Unreconciled suspense balances</t>
+          <t>Bypass rate not measured</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2050,13 +2050,13 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="16" t="n"/>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>TL05</t>
+          <t>TL04</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
@@ -2066,22 +2066,22 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Data export for lender reporting</t>
+          <t>Mobile money integration and reconciliation</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Sample monthly export</t>
+          <t>Payment platform to ledger reconciliation</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Spreadsheets maintained by hand as the primary record</t>
+          <t>Unreconciled suspense balances</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2093,38 +2093,38 @@
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="16" t="n"/>
       <c r="K31" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>FI01</t>
+          <t>TL05</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Finance and accounting</t>
+          <t>Technology and lockout</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Audited and management accounts</t>
+          <t>Data export for lender reporting</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Last audited accounts; monthly management accounts</t>
+          <t>Sample monthly export</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Audit qualification or late filing</t>
+          <t>Spreadsheets maintained by hand as the primary record</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2136,13 +2136,13 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="16" t="n"/>
       <c r="K32" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>FI02</t>
+          <t>FI01</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
@@ -2152,17 +2152,17 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Revenue recognition policy</t>
+          <t>Audited and management accounts</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Policy note; auditor correspondence</t>
+          <t>Last audited accounts; monthly management accounts</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Whole contract value booked as revenue at sale</t>
+          <t>Audit qualification or late filing</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -2179,13 +2179,13 @@
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="16" t="n"/>
       <c r="K33" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>FI03</t>
+          <t>FI02</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>ECL methodology and staging</t>
+          <t>Revenue recognition policy</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>ECL policy and model; auditor view</t>
+          <t>Policy note; auditor correspondence</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Allowance flat while PAR30 rises</t>
+          <t>Whole contract value booked as revenue at sale</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>FI04</t>
+          <t>FI03</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Budget against actual</t>
+          <t>ECL methodology and staging</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Budgets and variance analysis</t>
+          <t>ECL policy and model; auditor view</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Collections systematically over forecast</t>
+          <t>Allowance flat while PAR30 rises</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -2265,13 +2265,13 @@
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="16" t="n"/>
       <c r="K35" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>FI05</t>
+          <t>FI04</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -2281,22 +2281,22 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>FX exposure map</t>
+          <t>Budget against actual</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Currency of costs, debt and revenue</t>
+          <t>Budgets and variance analysis</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Hard currency debt funding the receivables book, unhedged</t>
+          <t>Collections systematically over forecast</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -2308,13 +2308,13 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="16" t="n"/>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>FI06</t>
+          <t>FI05</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Funding requirement and plan</t>
+          <t>FX exposure map</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Monthly cash forecast</t>
+          <t>Currency of costs, debt and revenue</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Plan relies on facilities not yet signed</t>
+          <t>Hard currency debt funding the receivables book, unhedged</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -2351,13 +2351,13 @@
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="16" t="n"/>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>FI07</t>
+          <t>FI06</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
@@ -2367,22 +2367,22 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Tax position</t>
+          <t>Funding requirement and plan</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Tax filings; open audits</t>
+          <t>Monthly cash forecast</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Disputed VAT or duty exemptions</t>
+          <t>Plan relies on facilities not yet signed</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -2394,38 +2394,38 @@
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="16" t="n"/>
       <c r="K38" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>LG01</t>
+          <t>FI07</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Legal and regulatory</t>
+          <t>Finance and accounting</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Lending and consumer credit licences</t>
+          <t>Tax position</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Licences; local counsel opinion</t>
+          <t>Tax filings; open audits</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Lending activity without the required licence</t>
+          <t>Disputed VAT or duty exemptions</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>LG02</t>
+          <t>LG01</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
@@ -2453,22 +2453,22 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Pricing disclosure and APR</t>
+          <t>Lending and consumer credit licences</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Disclosure samples; APR schedule by plan</t>
+          <t>Licences; local counsel opinion</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>APR never computed by the company</t>
+          <t>Lending activity without the required licence</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>LG03</t>
+          <t>LG02</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Collection conduct and lockout rules</t>
+          <t>Pricing disclosure and APR</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Collections policy; counsel review</t>
+          <t>Disclosure samples; APR schedule by plan</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Lockout practices not reviewed by counsel</t>
+          <t>APR never computed by the company</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -2529,7 +2529,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>LG04</t>
+          <t>LG03</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
@@ -2539,17 +2539,17 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Data protection</t>
+          <t>Collection conduct and lockout rules</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Consent forms; registrations</t>
+          <t>Collections policy; counsel review</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>No consent for the use of data in underwriting</t>
+          <t>Lockout practices not reviewed by counsel</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>LG05</t>
+          <t>LG04</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
@@ -2582,22 +2582,22 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Facility and security documents</t>
+          <t>Data protection</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Facility agreements; compliance certificates</t>
+          <t>Consent forms; registrations</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Waivers requested in the last twelve months</t>
+          <t>No consent for the use of data in underwriting</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -2609,13 +2609,13 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="16" t="n"/>
       <c r="K43" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>LG06</t>
+          <t>LG05</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Exchange control and repatriation</t>
+          <t>Facility and security documents</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Counsel opinion; investment registrations</t>
+          <t>Facility agreements; compliance certificates</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Foreign investment or loans not registered</t>
+          <t>Waivers requested in the last twelve months</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -2652,13 +2652,13 @@
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="16" t="n"/>
       <c r="K44" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>LG07</t>
+          <t>LG06</t>
         </is>
       </c>
       <c r="B45" s="15" t="inlineStr">
@@ -2668,22 +2668,22 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>True sale and securitisation feasibility, if relevant</t>
+          <t>Exchange control and repatriation</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Counsel memo</t>
+          <t>Counsel opinion; investment registrations</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>No opinion obtained</t>
+          <t>Foreign investment or loans not registered</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -2695,38 +2695,38 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="16" t="n"/>
       <c r="K45" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>ES01</t>
+          <t>LG07</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>ESG and consumer protection</t>
+          <t>Legal and regulatory</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Payment burden by tier</t>
+          <t>True sale and securitisation feasibility, if relevant</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Consumer_Risk based on surveyed incomes</t>
+          <t>Counsel memo</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Illustrative incomes still in use</t>
+          <t>No opinion obtained</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -2738,13 +2738,13 @@
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="16" t="n"/>
       <c r="K46" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>ES02</t>
+          <t>ES01</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Complaints handling</t>
+          <t>Payment burden by tier</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Complaints log and resolution times</t>
+          <t>Consumer_Risk based on surveyed incomes</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>No complaints log</t>
+          <t>Illustrative incomes still in use</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -2781,13 +2781,13 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="16" t="n"/>
       <c r="K47" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>ES03</t>
+          <t>ES02</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Hardship and restructuring treatment</t>
+          <t>Complaints handling</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Written policy</t>
+          <t>Complaints log and resolution times</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Restructuring used to hide arrears</t>
+          <t>No complaints log</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>ES04</t>
+          <t>ES03</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
@@ -2840,22 +2840,22 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>E-waste and battery take back</t>
+          <t>Hardship and restructuring treatment</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Take back process; recycler contracts</t>
+          <t>Written policy</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>No end of life process</t>
+          <t>Restructuring used to hide arrears</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>ES05</t>
+          <t>ES04</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
@@ -2883,22 +2883,22 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Ownership tracking</t>
+          <t>E-waste and battery take back</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Unlock records at the end of tenor</t>
+          <t>Take back process; recycler contracts</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Ownership claimed without evidence</t>
+          <t>No end of life process</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -2910,38 +2910,38 @@
       <c r="I50" s="10" t="n"/>
       <c r="J50" s="16" t="n"/>
       <c r="K50" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>MG01</t>
+          <t>ES05</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Management and governance</t>
+          <t>ESG and consumer protection</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Credit function authority</t>
+          <t>Ownership tracking</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Organisation chart; credit committee minutes</t>
+          <t>Unlock records at the end of tenor</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Sales leadership sets credit policy</t>
+          <t>Ownership claimed without evidence</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -2953,13 +2953,13 @@
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="16" t="n"/>
       <c r="K51" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>MG02</t>
+          <t>MG01</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Finance team capacity</t>
+          <t>Credit function authority</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Organisation chart; CVs</t>
+          <t>Organisation chart; credit committee minutes</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Monthly reconciliations not produced</t>
+          <t>Sales leadership sets credit policy</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>MG03</t>
+          <t>MG02</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
@@ -3012,22 +3012,22 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Board reporting</t>
+          <t>Finance team capacity</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>Recent board packs</t>
+          <t>Organisation chart; CVs</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>Board packs without cohort curves</t>
+          <t>Monthly reconciliations not produced</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>MG04</t>
+          <t>MG03</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Incentives and key person risk</t>
+          <t>Board reporting</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Incentive plans; succession</t>
+          <t>Recent board packs</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Incentives on sales volume only</t>
+          <t>Board packs without cohort curves</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
@@ -3088,7 +3088,7 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>MG05</t>
+          <t>MG04</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
@@ -3098,17 +3098,17 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Related party transactions</t>
+          <t>Incentives and key person risk</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>Related party register</t>
+          <t>Incentive plans; succession</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>Undisclosed related party supply</t>
+          <t>Incentives on sales volume only</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -3128,9 +3128,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>MG05</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Management and governance</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Related party transactions</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Related party register</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>Undisclosed related party supply</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="12" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:K55"/>
-  <conditionalFormatting sqref="G7:G55">
+  <autoFilter ref="A6:K56"/>
+  <conditionalFormatting sqref="G7:G56">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$G7="Issue found"</formula>
     </cfRule>
@@ -3139,10 +3182,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="F7:F55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7:F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G7:G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Requested,Received,Under review,Issue found,Closed,Not applicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3151,7 +3194,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T02&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T02 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3182,7 +3225,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3224,7 +3267,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T02  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T02  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -3285,23 +3328,23 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A7)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A7)</f>
         <v/>
       </c>
       <c r="C7" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D7" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E7" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F7" s="18">
-        <f>C7-COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A7,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C7-COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A7,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G7" s="19">
@@ -3320,23 +3363,23 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A8)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A8)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E8" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F8" s="18">
-        <f>C8-COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A8,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C8-COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A8,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G8" s="19">
@@ -3355,23 +3398,23 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A9)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A9)</f>
         <v/>
       </c>
       <c r="C9" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D9" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F9" s="18">
-        <f>C9-COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A9,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C9-COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A9,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G9" s="19">
@@ -3390,23 +3433,23 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A10)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A10)</f>
         <v/>
       </c>
       <c r="C10" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D10" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>C10-COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A10,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C10-COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A10,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G10" s="19">
@@ -3425,23 +3468,23 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A11)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A11)</f>
         <v/>
       </c>
       <c r="C11" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D11" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F11" s="18">
-        <f>C11-COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A11,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C11-COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A11,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G11" s="19">
@@ -3460,23 +3503,23 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A12)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A12)</f>
         <v/>
       </c>
       <c r="C12" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D12" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F12" s="18">
-        <f>C12-COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A12,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C12-COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A12,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G12" s="19">
@@ -3495,23 +3538,23 @@
         </is>
       </c>
       <c r="B13" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A13)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A13)</f>
         <v/>
       </c>
       <c r="C13" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>C13-COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A13,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C13-COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A13,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G13" s="19">
@@ -3530,23 +3573,23 @@
         </is>
       </c>
       <c r="B14" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A14)</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A14)</f>
         <v/>
       </c>
       <c r="C14" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$F$7:$F$55,"High")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$F$7:$F$56,"High")</f>
         <v/>
       </c>
       <c r="D14" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$G$7:$G$55,"Closed")+COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$G$7:$G$56,"Closed")+COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$G$7:$G$55,"Issue found")</f>
+        <f>COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$G$7:$G$56,"Issue found")</f>
         <v/>
       </c>
       <c r="F14" s="18">
-        <f>C14-COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Closed")-COUNTIFS(Checklist!$B$7:$B$55,A14,Checklist!$F$7:$F$55,"High",Checklist!$G$7:$G$55,"Not applicable")</f>
+        <f>C14-COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Closed")-COUNTIFS(Checklist!$B$7:$B$56,A14,Checklist!$F$7:$F$56,"High",Checklist!$G$7:$G$56,"Not applicable")</f>
         <v/>
       </c>
       <c r="G14" s="19">
@@ -3692,7 +3735,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T02&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T02 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
